--- a/app/static/templates/excel/template_lessons.xlsx
+++ b/app/static/templates/excel/template_lessons.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lessons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lessons" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/app/static/templates/excel/template_lessons.xlsx
+++ b/app/static/templates/excel/template_lessons.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,19 @@
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="37" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +508,71 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>thumbnail_url</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>audio_url</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>accent</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>audio_duration</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>listening_transcript</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>reading_genre</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>reading_passage</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>speaking_genre</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>speaking_sentences</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>speaking_tips</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>writing_genre</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>min_words</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>max_words</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>writing_templates</t>
         </is>
       </c>
     </row>
@@ -543,6 +621,37 @@
           <t>https://images.unsplash.com/photo-1516321318423-f06f85e504b3?w=500</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Email công việc (Business Email)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Lời chào &amp; Mở đầu | I hope this email finds you well. | Hy vọng bạn nhận được email này trong tình trạng tốt nhất.
+Yêu cầu | Could you please provide the latest update on the project? | Bạn có thể vui lòng cập nhật tiến độ mới nhất của dự án không?
+Kết thư | Thank you for your support and collaboration. | Cảm ơn sự hỗ trợ và hợp tác của bạn.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -584,6 +693,33 @@
           <t>https://images.unsplash.com/photo-1522202176988-66273c2fd55f?w=500</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Giao tiếp thường ngày (Daily Small Talk)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Nice weather we're having today, isn't it? | /naɪs ˈweð.ɚ wiːr ˈhæv.ɪŋ təˈdeɪ/ | Thời tiết hôm nay đẹp thật, phải không?
+How are things going with your new team? | /haʊ ɑːr θɪŋz ˈɡoʊ.ɪŋ wɪð jɔːr nuː tiːm/ | Mọi chuyện với nhóm mới của bạn thế nào rồi?</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Giữ ngữ điệu thân thiện và mỉm cười khi mở đầu cuộc trò chuyện.
+Chú ý nối âm giữa các từ kết thúc bằng phụ âm và bắt đầu bằng nguyên âm.</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
